--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="550" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>idx</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>Language</t>
+  </si>
+  <si>
+    <t>자수정 방패</t>
+  </si>
+  <si>
+    <t>Amethyst Shield</t>
   </si>
 </sst>
 </file>
@@ -993,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1173,33 +1179,21 @@
       <c r="A13" s="1">
         <v>10011</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>10012</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>10013</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>10014</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
@@ -1216,172 +1210,18 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="A18" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="550" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>idx</t>
   </si>
@@ -120,6 +120,30 @@
   </si>
   <si>
     <t>Amethyst Shield</t>
+  </si>
+  <si>
+    <t>공격력</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>방어력</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>체력</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>기력</t>
+  </si>
+  <si>
+    <t>Stamina</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1197,29 +1221,160 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>20001</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
+        <v>10016</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1">
+        <v>10017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1">
+        <v>10018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1">
+        <v>10019</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1">
+        <v>10020</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1">
+        <v>10021</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1">
+        <v>10022</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
+        <v>10023</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
+        <v>10025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1">
+        <v>10026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1">
+        <v>10027</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1">
+        <v>10029</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1">
+        <v>10030</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1">
+        <v>10031</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1">
+        <v>10032</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1">
+        <v>10033</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1">
         <v>20002</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>31</v>
       </c>
     </row>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>idx</t>
   </si>
@@ -144,6 +144,30 @@
   </si>
   <si>
     <t>Stamina</t>
+  </si>
+  <si>
+    <t>모험가에게 가장 기본적으로 필요한 무기 중 하나.</t>
+  </si>
+  <si>
+    <t>One of the most basic weapons an adventurer needs.</t>
+  </si>
+  <si>
+    <t>Made of hard amethyst, it provides excellent defense.</t>
+  </si>
+  <si>
+    <t>단단한 자수정으로 만들어져 방어력이 뛰어나다.</t>
+  </si>
+  <si>
+    <t>공격속도</t>
+  </si>
+  <si>
+    <t>공격범위</t>
+  </si>
+  <si>
+    <t>Attack Speed</t>
+  </si>
+  <si>
+    <t>Attack Range</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1047,335 +1071,481 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1">
-        <v>10000</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
-        <v>10001</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1">
-        <v>10002</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
-        <v>10003</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
-        <v>10004</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
-        <v>10005</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
-        <v>10006</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
-        <v>10007</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
-        <v>10008</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
-        <v>10009</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
-        <v>10010</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
-        <v>10011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
-        <v>10012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
-        <v>10013</v>
+        <v>10000</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
-        <v>10014</v>
+        <v>10001</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>10015</v>
+        <v>10002</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
-        <v>10016</v>
+        <v>10003</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
-        <v>10017</v>
+        <v>10004</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
-        <v>10018</v>
+        <v>10005</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
-        <v>10019</v>
+        <v>10006</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
-        <v>10020</v>
+        <v>10007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
-        <v>10021</v>
+        <v>10008</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
-        <v>10022</v>
+        <v>10009</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
-        <v>10023</v>
+        <v>10010</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
-        <v>10024</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
-        <v>10025</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
-        <v>10026</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
-        <v>10027</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
-        <v>10028</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
-        <v>10029</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
-        <v>10030</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>10031</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
-        <v>10032</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>10033</v>
+        <v>10020</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>20001</v>
+        <v>10021</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
+        <v>10022</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1">
+        <v>10023</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1">
+        <v>10024</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1">
+        <v>10025</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1">
+        <v>10026</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1">
+        <v>10027</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1">
+        <v>10028</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1">
+        <v>10029</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1">
+        <v>10030</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1">
+        <v>10031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1">
+        <v>10032</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1">
+        <v>10033</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1">
         <v>20002</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1">
+        <v>101001</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1">
+        <v>101002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1">
+        <v>101003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
+        <v>101004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
+        <v>101005</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
+        <v>102001</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
+        <v>102002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1">
+        <v>102003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1">
+        <v>102004</v>
       </c>
     </row>
   </sheetData>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="테이블" sheetId="1" r:id="rId1"/>
+    <sheet name="인덱스 목록" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>idx</t>
   </si>
@@ -168,6 +168,63 @@
   </si>
   <si>
     <t>Attack Range</t>
+  </si>
+  <si>
+    <t>1001~1999</t>
+  </si>
+  <si>
+    <t>무기</t>
+  </si>
+  <si>
+    <t>2001~2999</t>
+  </si>
+  <si>
+    <t>방패</t>
+  </si>
+  <si>
+    <t>3001~4999</t>
+  </si>
+  <si>
+    <t>액세서리</t>
+  </si>
+  <si>
+    <t>101001~104999</t>
+  </si>
+  <si>
+    <t>아이템 설명</t>
+  </si>
+  <si>
+    <t>10001~29999</t>
+  </si>
+  <si>
+    <t>게임 텍스트</t>
+  </si>
+  <si>
+    <t>게임 UI 텍스트</t>
+  </si>
+  <si>
+    <t>30000~49999</t>
+  </si>
+  <si>
+    <t>몬스터 이름</t>
+  </si>
+  <si>
+    <t>130000~149999</t>
+  </si>
+  <si>
+    <t>몬스터 설명?</t>
+  </si>
+  <si>
+    <t>스켈레톤</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>타락자</t>
+  </si>
+  <si>
+    <t>Fallen</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1073,6 +1130,15 @@
       <c r="A2" s="1">
         <v>1001</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
@@ -1136,415 +1202,457 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
-        <v>10000</v>
+        <v>2001</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
-        <v>10011</v>
+        <v>10010</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
-        <v>10019</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>10020</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>33</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>10021</v>
+        <v>10020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1">
-        <v>10023</v>
+        <v>10022</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1">
-        <v>10024</v>
+        <v>10023</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1">
-        <v>10025</v>
+        <v>10024</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1">
-        <v>10026</v>
+        <v>10025</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1">
-        <v>10027</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1">
-        <v>10028</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1">
-        <v>10029</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1">
-        <v>10030</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
-        <v>10031</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>20001</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
-        <v>101001</v>
+        <v>20002</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>101002</v>
+        <v>30001</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
-        <v>101003</v>
+        <v>30002</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1">
-        <v>101004</v>
+        <v>101001</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1">
-        <v>101005</v>
+        <v>101002</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
-        <v>102001</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>101003</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
-        <v>102002</v>
+        <v>101004</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>102003</v>
+        <v>101005</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
+        <v>102001</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1">
+        <v>102002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1">
+        <v>102003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1">
         <v>102004</v>
       </c>
     </row>
@@ -1558,9 +1666,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A2:B9"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.12999916" customWidth="1" outlineLevel="0"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="520" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="테이블" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,15 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors/>
+  <commentList/>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>idx</t>
   </si>
@@ -225,6 +232,99 @@
   </si>
   <si>
     <t>Fallen</t>
+  </si>
+  <si>
+    <t>5000~5001</t>
+  </si>
+  <si>
+    <t>유니크 무기</t>
+  </si>
+  <si>
+    <t>5000~5999</t>
+  </si>
+  <si>
+    <t>6000~6999</t>
+  </si>
+  <si>
+    <t>유니크 방패</t>
+  </si>
+  <si>
+    <t>7000~7999</t>
+  </si>
+  <si>
+    <t>유니크 액세서리</t>
+  </si>
+  <si>
+    <t>101001~107999</t>
+  </si>
+  <si>
+    <t>90000~99999</t>
+  </si>
+  <si>
+    <t>아이템 추가옵션</t>
+  </si>
+  <si>
+    <t>90000~94999</t>
+  </si>
+  <si>
+    <t>95000~99999</t>
+  </si>
+  <si>
+    <t>아이템 추가 고유옵션</t>
+  </si>
+  <si>
+    <t>추가 공격력 +{0}</t>
+  </si>
+  <si>
+    <t>추가 공격력 +{0}%</t>
+  </si>
+  <si>
+    <t>{0} 속성 공격력 +{1}</t>
+  </si>
+  <si>
+    <t>추가 공격력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t>{0} 속성 공격력 +{1}% 증가</t>
+  </si>
+  <si>
+    <t>추가 방어력 +{0}</t>
+  </si>
+  <si>
+    <t>추가 방어력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 땅을 타는 불꽃 생성</t>
+  </si>
+  <si>
+    <t>공격시 +{0}% 확률로 {1}</t>
+  </si>
+  <si>
+    <t>땅을 타는 불꽃 생성</t>
+  </si>
+  <si>
+    <t>Additional Attack Damage +{0}</t>
+  </si>
+  <si>
+    <t>Additional Attack Damage +{0}%</t>
+  </si>
+  <si>
+    <t>create flames that travel along the ground</t>
+  </si>
+  <si>
+    <t>{0}% chance on attack to {1}</t>
+  </si>
+  <si>
+    <t>Additional Defense +{0}%</t>
+  </si>
+  <si>
+    <t>Additional Defense +{0}</t>
+  </si>
+  <si>
+    <t>{0} Damage +{1}%</t>
+  </si>
+  <si>
+    <t>{0} Damage +{1}</t>
   </si>
 </sst>
 </file>
@@ -776,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -784,6 +884,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1104,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1595,64 +1701,212 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1">
-        <v>101001</v>
+        <v>90001</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1">
-        <v>101002</v>
+        <v>90002</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
-        <v>101003</v>
+        <v>90003</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
-        <v>101004</v>
+        <v>90004</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>101005</v>
+        <v>90005</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>102001</v>
+        <v>90006</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
-        <v>102002</v>
+        <v>90007</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>102003</v>
+        <v>90008</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
+        <v>90009</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1">
+        <v>90010</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1">
+        <v>90011</v>
+      </c>
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1">
+        <v>90012</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1">
+        <v>95001</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1">
+        <v>95002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1">
+        <v>95003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1">
+        <v>101001</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1">
+        <v>101002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1">
+        <v>101003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1">
+        <v>101004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1">
+        <v>101005</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1">
+        <v>102001</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1">
+        <v>102002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1">
+        <v>102003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1">
         <v>102004</v>
       </c>
     </row>
@@ -1666,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:B9"/>
+  <dimension ref="A2:B15"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" width="21.12999916" customWidth="1" outlineLevel="0"/>
@@ -1698,33 +1952,73 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="0" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="0" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B15" s="0" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1732,6 +2026,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="520" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="510" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="테이블" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>idx</t>
   </si>
@@ -325,6 +325,64 @@
   </si>
   <si>
     <t>{0} Damage +{1}</t>
+  </si>
+  <si>
+    <t>화염 속성 공격력 +{1}</t>
+  </si>
+  <si>
+    <t>화염 속성 공격력 +{1}% 증가</t>
+  </si>
+  <si>
+    <t>냉기 속성 공격력 +{1}</t>
+  </si>
+  <si>
+    <t>냉기 속성 공격력 +{1}% 증가</t>
+  </si>
+  <si>
+    <t>독 속성 공격력 +{1}</t>
+  </si>
+  <si>
+    <t>독 속성 공격력 +{1}% 증가</t>
+  </si>
+  <si>
+    <t>공격시 +{0}% 확률로 땅을 타는 불꽃 생성</t>
+  </si>
+  <si>
+    <t>화염 속성 공격력 +{0}</t>
+  </si>
+  <si>
+    <t>화염 속성 공격력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t>냉기 속성 공격력 +{0}</t>
+  </si>
+  <si>
+    <t>냉기 속성 공격력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t>독 속성 공격력 +{0}</t>
+  </si>
+  <si>
+    <t>독 속성 공격력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t>Fire Damage +{0}</t>
+  </si>
+  <si/>
+  <si>
+    <t>Ice Damage +{0}</t>
+  </si>
+  <si>
+    <t>Poison Damage +{0}</t>
+  </si>
+  <si>
+    <t>Poison Damage +{0}%</t>
+  </si>
+  <si>
+    <t>Ice Damage +{0}%</t>
+  </si>
+  <si>
+    <t>Fire Damage +{0}%</t>
   </si>
 </sst>
 </file>
@@ -876,7 +934,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,6 +949,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1210,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1700,10 +1764,10 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="1">
+      <c r="A54" s="5">
         <v>90001</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -1714,10 +1778,10 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="1">
+      <c r="A55" s="5">
         <v>90002</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -1728,185 +1792,259 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="1">
+      <c r="A56" s="5">
         <v>90003</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>82</v>
+      <c r="B56" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1">
+      <c r="A57" s="5">
         <v>90004</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>84</v>
+      <c r="B57" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="1">
+      <c r="A58" s="5">
         <v>90005</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="5">
+        <v>90006</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="5">
+        <v>90007</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="5">
+        <v>90008</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="6">
+        <v>90009</v>
+      </c>
+      <c r="B62" s="6"/>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="6">
+        <v>90010</v>
+      </c>
+      <c r="B63" s="6"/>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="6">
+        <v>90011</v>
+      </c>
+      <c r="B64" s="6"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="6">
+        <v>90012</v>
+      </c>
+      <c r="B65" s="6"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="6">
+        <v>90013</v>
+      </c>
+      <c r="B66" s="6"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="6">
+        <v>90014</v>
+      </c>
+      <c r="B67" s="6"/>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="6">
+        <v>90015</v>
+      </c>
+      <c r="B68" s="6"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="6">
+        <v>91001</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="1">
-        <v>90006</v>
-      </c>
-      <c r="B59" s="1" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" s="6">
+        <v>91002</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="1">
-        <v>90007</v>
-      </c>
-      <c r="B60" s="1" t="s">
+    <row r="71" spans="1:4">
+      <c r="A71" s="6">
+        <v>92000</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="1">
-        <v>90008</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="1">
-        <v>90009</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="1">
-        <v>90010</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="1">
-        <v>90011</v>
-      </c>
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="1">
-        <v>90012</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="1">
-        <v>95001</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="1">
-        <v>95002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="1">
-        <v>95003</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1">
-        <v>101001</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1">
-        <v>101002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="1">
-        <v>101003</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1">
-        <v>101004</v>
+        <v>95001</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="1">
-        <v>101005</v>
-      </c>
+        <v>95002</v>
+      </c>
+      <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1">
-        <v>102001</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>95003</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1">
-        <v>102002</v>
+        <v>101001</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1">
-        <v>102003</v>
+        <v>101002</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1">
+        <v>101003</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1">
+        <v>101004</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1">
+        <v>101005</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1">
+        <v>102001</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1">
+        <v>102002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1">
+        <v>102003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="1">
         <v>102004</v>
       </c>
     </row>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="510" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="500" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="테이블" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>idx</t>
   </si>
@@ -383,6 +383,51 @@
   </si>
   <si>
     <t>Fire Damage +{0}%</t>
+  </si>
+  <si>
+    <t>잿불가지</t>
+  </si>
+  <si>
+    <t>Ember Branch</t>
+  </si>
+  <si>
+    <t>Infernal Vine</t>
+  </si>
+  <si>
+    <t>화염 덩굴</t>
+  </si>
+  <si>
+    <t>불길은 오래전에 꺼졌지만, 닿는 모든 것들을 재로 만드는 검.</t>
+  </si>
+  <si>
+    <t>불길은 오래전에 꺼졌지만, 닿는 모든 것들을 재로 만드는 검</t>
+  </si>
+  <si>
+    <t>불길이 몸을 휘감는 듯 하다.</t>
+  </si>
+  <si>
+    <t>불길이 덩굴처럼 몸을 휘감는 듯 하다. 설마 살아있나?</t>
+  </si>
+  <si>
+    <t>The flames coil around its wielder like living vines. Could they actually be alive?</t>
+  </si>
+  <si>
+    <t>The flames died out long ago, yet the blade still turns everything it touches to ash.</t>
+  </si>
+  <si>
+    <t>{0}% chance on attack to spawn flames that travel along the ground.</t>
+  </si>
+  <si>
+    <t>추가 체력 +{0}</t>
+  </si>
+  <si>
+    <t>추가 체력 +{0}% 증가</t>
+  </si>
+  <si>
+    <t>Health +{0}</t>
+  </si>
+  <si>
+    <t>Health +{0}%</t>
   </si>
 </sst>
 </file>
@@ -934,7 +979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -949,9 +994,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1274,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
@@ -1386,666 +1428,741 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
-        <v>10001</v>
+        <v>7000</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>6</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
-        <v>10002</v>
+        <v>10000</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
-        <v>10009</v>
+        <v>10007</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
-        <v>10010</v>
+        <v>10008</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
-        <v>10011</v>
+        <v>10009</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
-        <v>10012</v>
+        <v>10010</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
-        <v>10013</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
-        <v>10014</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
-        <v>10015</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
-        <v>10016</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>10017</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
-        <v>10018</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>10019</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>10020</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>33</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
-        <v>10021</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>35</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1">
-        <v>10022</v>
+        <v>10020</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1">
-        <v>10023</v>
+        <v>10021</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1">
-        <v>10024</v>
+        <v>10022</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1">
-        <v>10025</v>
+        <v>10023</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1">
-        <v>10026</v>
+        <v>10024</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1">
-        <v>10027</v>
+        <v>10025</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1">
-        <v>10028</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1">
-        <v>10029</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
-        <v>10030</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
-        <v>10031</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1">
-        <v>10032</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
-        <v>10033</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
-        <v>20001</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
-        <v>20002</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>31</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1">
+        <v>30001</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1">
         <v>30002</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="5">
+    <row r="56" spans="1:4">
+      <c r="A56" s="1">
         <v>90001</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B56" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="5">
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
         <v>90002</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B57" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="5">
+    <row r="58" spans="1:4">
+      <c r="A58" s="1">
         <v>90003</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B58" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="5">
+    <row r="59" spans="1:4">
+      <c r="A59" s="1">
         <v>90004</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="5">
+    <row r="60" spans="1:4">
+      <c r="A60" s="1">
         <v>90005</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B60" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="5">
+    <row r="61" spans="1:4">
+      <c r="A61" s="1">
         <v>90006</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="5">
+    <row r="62" spans="1:4">
+      <c r="A62" s="1">
         <v>90007</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B62" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="5">
+    <row r="63" spans="1:4">
+      <c r="A63" s="1">
         <v>90008</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B63" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="6">
+    <row r="64" spans="1:4">
+      <c r="A64" s="1">
         <v>90009</v>
       </c>
-      <c r="B62" s="6"/>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="6">
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1">
         <v>90010</v>
       </c>
-      <c r="B63" s="6"/>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="6">
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1">
         <v>90011</v>
       </c>
-      <c r="B64" s="6"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="6">
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1">
         <v>90012</v>
       </c>
-      <c r="B65" s="6"/>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="6">
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1">
         <v>90013</v>
       </c>
-      <c r="B66" s="6"/>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="6">
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1">
         <v>90014</v>
       </c>
-      <c r="B67" s="6"/>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="6">
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1">
         <v>90015</v>
       </c>
-      <c r="B68" s="6"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="6">
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1">
         <v>91001</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B71" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="6">
-        <v>91002</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="6">
-        <v>92000</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1">
-        <v>95001</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>104</v>
+        <v>91002</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="1">
-        <v>95002</v>
-      </c>
-      <c r="B73" s="1"/>
+      <c r="A73" s="5">
+        <v>92001</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1">
-        <v>95003</v>
-      </c>
-      <c r="B74" s="1"/>
+      <c r="A74" s="5">
+        <v>92002</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1">
-        <v>101001</v>
+        <v>93000</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1">
-        <v>101002</v>
+        <v>95001</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1">
-        <v>101003</v>
+        <v>95002</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1">
-        <v>101004</v>
+        <v>95003</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="1">
-        <v>101005</v>
+        <v>101001</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="1">
+        <v>101002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1">
+        <v>101003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1">
+        <v>101004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1">
+        <v>101005</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1">
         <v>102001</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="1">
+    <row r="85" spans="1:4">
+      <c r="A85" s="1">
         <v>102002</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="1">
+    <row r="86" spans="1:4">
+      <c r="A86" s="1">
         <v>102003</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="1">
+    <row r="87" spans="1:4">
+      <c r="A87" s="1">
         <v>102004</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1">
+        <v>105000</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1">
+        <v>107000</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>idx</t>
   </si>
@@ -428,6 +428,18 @@
   </si>
   <si>
     <t>Health +{0}%</t>
+  </si>
+  <si>
+    <t>착용자 주위 화염 데미지에 비례한 불꽃 고리 생성</t>
+  </si>
+  <si>
+    <t>이 화염은 덩굴처럼 몸을 휘감는 듯 하다. 설마 살아있나?</t>
+  </si>
+  <si>
+    <t>Creates a ring of fire around the wearer, with damage scaling based on Fire Damage.</t>
+  </si>
+  <si>
+    <t>This fire seems to coil around the body like vines. Could it actually be alive?</t>
   </si>
 </sst>
 </file>
@@ -2068,6 +2080,15 @@
       <c r="A77" s="1">
         <v>95002</v>
       </c>
+      <c r="B77" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1">
@@ -2156,13 +2177,13 @@
         <v>107000</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>idx</t>
   </si>
@@ -440,6 +440,36 @@
   </si>
   <si>
     <t>This fire seems to coil around the body like vines. Could it actually be alive?</t>
+  </si>
+  <si>
+    <t>아이템을 버리시겠습니까?</t>
+  </si>
+  <si>
+    <t>네</t>
+  </si>
+  <si>
+    <t>아니오</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Are you sure you want to discard this item?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to\ndiscard this item?</t>
+  </si>
+  <si>
+    <t>새 게임을 시작하시겠습니까?</t>
+  </si>
+  <si>
+    <t>새 게임을 시작하시겠습니까?\n(기존 데이터는 삭제됩니다)</t>
+  </si>
+  <si>
+    <t>Would you like to start a new game?\n(Existing save data will be deleted.)</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1006,9 +1036,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1624,21 +1651,57 @@
       <c r="A29" s="1">
         <v>10011</v>
       </c>
+      <c r="B29" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
         <v>10012</v>
       </c>
+      <c r="B30" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
         <v>10013</v>
       </c>
+      <c r="B31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
         <v>10014</v>
       </c>
+      <c r="B32" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
@@ -2021,10 +2084,10 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="5">
+      <c r="A73" s="1">
         <v>92001</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -2035,10 +2098,10 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="5">
+      <c r="A74" s="1">
         <v>92002</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C74" s="1" t="s">

--- a/문서/contents.xlsx
+++ b/문서/contents.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>idx</t>
   </si>
@@ -470,6 +470,12 @@
   </si>
   <si>
     <t>Would you like to start a new game?\n(Existing save data will be deleted.)</t>
+  </si>
+  <si>
+    <t>탈출을 성공하였습니다!</t>
+  </si>
+  <si>
+    <t>Escape Successful!</t>
   </si>
 </sst>
 </file>
@@ -1707,6 +1713,15 @@
       <c r="A33" s="1">
         <v>10015</v>
       </c>
+      <c r="B33" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
